--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -89,6 +89,18 @@
   </x:si>
   <x:si>
     <x:t>BA 019/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 004/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reed Richard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 007/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -676,6 +688,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="A10" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -101,6 +101,12 @@
   </x:si>
   <x:si>
     <x:t>BA 007/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 022/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -740,6 +746,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8">
+      <x:c r="A13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -107,6 +107,12 @@
   </x:si>
   <x:si>
     <x:t>BA 022/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 027/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-18</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -798,6 +804,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" spans="1:8">
+      <x:c r="A14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -113,6 +113,15 @@
   </x:si>
   <x:si>
     <x:t>2026-06-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 029/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 030/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 031/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -830,6 +839,84 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:8">
+      <x:c r="A15" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:8">
+      <x:c r="A16" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:8">
+      <x:c r="A17" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -125,6 +125,9 @@
   </x:si>
   <x:si>
     <x:t>BA 034/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 035/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -946,6 +949,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" spans="1:8">
+      <x:c r="A19" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -128,6 +128,12 @@
   </x:si>
   <x:si>
     <x:t>BA 035/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 036/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-20</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -975,6 +981,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" spans="1:8">
+      <x:c r="A20" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -134,6 +134,24 @@
   </x:si>
   <x:si>
     <x:t>2026-06-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 037/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Peminjaman</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bucky Barnes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tony Stark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-02</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1007,6 +1025,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" spans="1:8">
+      <x:c r="A21" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -152,6 +152,18 @@
   </x:si>
   <x:si>
     <x:t>2026-07-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 040/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 041/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 042/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-26</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1051,6 +1063,84 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" spans="1:8">
+      <x:c r="A22" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:8">
+      <x:c r="A23" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:8">
+      <x:c r="A24" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -164,6 +164,9 @@
   </x:si>
   <x:si>
     <x:t>2026-06-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 043/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1141,6 +1144,32 @@
         <x:v>49</x:v>
       </x:c>
     </x:row>
+    <x:row r="25" spans="1:8">
+      <x:c r="A25" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -167,6 +167,21 @@
   </x:si>
   <x:si>
     <x:t>BA 043/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 025/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luthfi Alif Pramudya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 026/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-24</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1170,6 +1185,84 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" spans="1:8">
+      <x:c r="A26" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:8">
+      <x:c r="A27" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:8">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -182,6 +182,12 @@
   </x:si>
   <x:si>
     <x:t>2026-06-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 028/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sebastian Vettel</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1263,6 +1269,32 @@
         <x:v>55</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" spans="1:8">
+      <x:c r="A29" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -188,6 +188,9 @@
   </x:si>
   <x:si>
     <x:t>Sebastian Vettel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kimi Raikkonen</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1295,6 +1298,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" spans="1:8">
+      <x:c r="A30" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -191,6 +191,12 @@
   </x:si>
   <x:si>
     <x:t>Kimi Raikkonen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 032/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gus Fring</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1324,6 +1330,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" spans="1:8">
+      <x:c r="A31" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -197,6 +197,18 @@
   </x:si>
   <x:si>
     <x:t>Gus Fring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 033/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-27</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1356,6 +1368,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" spans="1:8">
+      <x:c r="A32" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:8">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -209,6 +209,21 @@
   </x:si>
   <x:si>
     <x:t>2026-06-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 001/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Romi Aprilian Mustafa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 002/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1420,6 +1435,58 @@
         <x:v>64</x:v>
       </x:c>
     </x:row>
+    <x:row r="34" spans="1:8">
+      <x:c r="A34" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:8">
+      <x:c r="A35" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -224,6 +224,12 @@
   </x:si>
   <x:si>
     <x:t>BA 002/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 005/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1487,6 +1493,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" spans="1:8">
+      <x:c r="A36" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -230,6 +230,15 @@
   </x:si>
   <x:si>
     <x:t>2026-07-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Walter White</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Peter Griffin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-10</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1519,6 +1528,32 @@
         <x:v>71</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" spans="1:8">
+      <x:c r="A37" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -239,6 +239,12 @@
   </x:si>
   <x:si>
     <x:t>2026-07-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 006/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 008/PPNEG1000/VI/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1554,6 +1560,84 @@
         <x:v>74</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" spans="1:8">
+      <x:c r="A38" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:8">
+      <x:c r="A39" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:8">
+      <x:c r="A40" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -245,6 +245,12 @@
   </x:si>
   <x:si>
     <x:t>BA 008/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 047/PPNEG1000/VI/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-30</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1638,6 +1644,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" spans="1:8">
+      <x:c r="A41" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -251,6 +251,12 @@
   </x:si>
   <x:si>
     <x:t>2026-06-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 018/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Penarikan</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1670,6 +1676,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="42" spans="1:8">
+      <x:c r="A42" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -257,6 +257,9 @@
   </x:si>
   <x:si>
     <x:t>Penarikan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 019/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1702,6 +1705,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="43" spans="1:8">
+      <x:c r="A43" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -260,6 +260,9 @@
   </x:si>
   <x:si>
     <x:t>BA 019/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 049/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1731,6 +1734,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" spans="1:8">
+      <x:c r="A44" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -263,6 +263,18 @@
   </x:si>
   <x:si>
     <x:t>BA 049/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 050/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lewis Hamilton</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eimi Fukada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 051/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1760,6 +1772,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="45" spans="1:8">
+      <x:c r="A45" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:8">
+      <x:c r="A46" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -275,6 +275,9 @@
   </x:si>
   <x:si>
     <x:t>BA 051/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 052/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1824,6 +1827,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="47" spans="1:8">
+      <x:c r="A47" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -278,6 +278,15 @@
   </x:si>
   <x:si>
     <x:t>BA 052/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 053/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 054/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-03</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1853,6 +1862,58 @@
         <x:v>68</x:v>
       </x:c>
     </x:row>
+    <x:row r="48" spans="1:8">
+      <x:c r="A48" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:8">
+      <x:c r="A49" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -287,6 +287,9 @@
   </x:si>
   <x:si>
     <x:t>2026-07-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 009/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1914,6 +1917,32 @@
         <x:v>90</x:v>
       </x:c>
     </x:row>
+    <x:row r="50" spans="1:8">
+      <x:c r="A50" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -290,6 +290,9 @@
   </x:si>
   <x:si>
     <x:t>BA 009/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 011/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1943,6 +1946,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="51" spans="1:8">
+      <x:c r="A51" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -287,6 +287,9 @@
   </x:si>
   <x:si>
     <x:t>2026-07-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 023/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1914,6 +1917,32 @@
         <x:v>90</x:v>
       </x:c>
     </x:row>
+    <x:row r="50" spans="1:8">
+      <x:c r="A50" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -290,6 +290,9 @@
   </x:si>
   <x:si>
     <x:t>BA 023/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 024/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1943,6 +1946,32 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
+    <x:row r="51" spans="1:8">
+      <x:c r="A51" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -293,6 +293,18 @@
   </x:si>
   <x:si>
     <x:t>BA 024/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 027/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 028/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 029/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 030/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1972,6 +1984,110 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="52" spans="1:8">
+      <x:c r="A52" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:8">
+      <x:c r="A53" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:8">
+      <x:c r="A54" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:8">
+      <x:c r="A55" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -305,6 +305,12 @@
   </x:si>
   <x:si>
     <x:t>BA 030/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 031/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 032/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2088,6 +2094,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="56" spans="1:8">
+      <x:c r="A56" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:8">
+      <x:c r="A57" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -311,6 +311,12 @@
   </x:si>
   <x:si>
     <x:t>BA 032/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 003/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 004/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2146,6 +2152,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="58" spans="1:8">
+      <x:c r="A58" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:8">
+      <x:c r="A59" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -317,6 +317,9 @@
   </x:si>
   <x:si>
     <x:t>BA 004/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 005/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2204,6 +2207,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="60" spans="1:8">
+      <x:c r="A60" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -311,6 +311,18 @@
   </x:si>
   <x:si>
     <x:t>BA 032/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 003/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 004/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA 005/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-016/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2146,6 +2158,110 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="58" spans="1:8">
+      <x:c r="A58" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:8">
+      <x:c r="A59" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:8">
+      <x:c r="A60" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:8">
+      <x:c r="A61" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -323,6 +323,12 @@
   </x:si>
   <x:si>
     <x:t>BA-016/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-001/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-05</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2262,6 +2268,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="62" spans="1:8">
+      <x:c r="A62" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -329,6 +329,15 @@
   </x:si>
   <x:si>
     <x:t>2026-07-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-002/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-09</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2294,6 +2303,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="63" spans="1:8">
+      <x:c r="A63" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -320,6 +320,15 @@
   </x:si>
   <x:si>
     <x:t>BA 005/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-033/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-034/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2233,6 +2242,58 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="61" spans="1:8">
+      <x:c r="A61" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:8">
+      <x:c r="A62" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -329,6 +329,12 @@
   </x:si>
   <x:si>
     <x:t>2026-07-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-001/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-12</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2294,6 +2300,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="63" spans="1:8">
+      <x:c r="A63" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -335,6 +335,21 @@
   </x:si>
   <x:si>
     <x:t>2026-07-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-005/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-006/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-007/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-008/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA-002/PPNEG1000/2026-S0</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2326,6 +2341,162 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="64" spans="1:8">
+      <x:c r="A64" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:8">
+      <x:c r="A65" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:8">
+      <x:c r="A66" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:8">
+      <x:c r="A67" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:8">
+      <x:c r="A68" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:8">
+      <x:c r="A69" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
+++ b/SistemBeritaAcara.Web/data/ArsipBeritaAcara.xlsx
@@ -350,6 +350,9 @@
   </x:si>
   <x:si>
     <x:t>BA-002/PPNEG1000/2026-S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-13</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2497,6 +2500,32 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="70" spans="1:8">
+      <x:c r="A70" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
